--- a/AI Audit Log_DoanTrongLuc.xlsx
+++ b/AI Audit Log_DoanTrongLuc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\!fpt\SU26\SWD392\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96877CCD-D045-481D-A865-85ED6F45D36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F96585E-46AC-4ED2-A7B2-9CDF7AC38B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
@@ -28,15 +28,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>“So sánh các giải thuật CPU scheduling: FCFS, SJF, Round Robin, Priority. Giải thuật nào tốt nhất?”</t>
-  </si>
-  <si>
-    <t>Ví dụ: Pattern Recognition + Literature Review</t>
-  </si>
-  <si>
-    <t>“Tóm tắt 5 bài báo gần đây nhất về anomaly detection trong IoT sensor data.”</t>
   </si>
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
@@ -57,9 +51,6 @@
   <si>
     <t>Phản hồi: AI tóm tắt 5 papers với tên tác giả, năm xuất bản và tóm tắt nội dung.
 Kiểm chứng: Tìm trên Google Scholar: 2/5 papers AI nêu là không tồn tại (fabrication). Tôi đã thay bằng 2 papers mà tôi đã tìm kiếm trên research gates và đã kiểm chứng trên google scholar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ví dụ: </t>
   </si>
   <si>
     <t xml:space="preserve">Discuss what these sources say about Object-Oriented Methods, in the larger context of Core Concepts.
@@ -86,13 +77,164 @@
     <t>AI response : - Software architecture is the high-level design that separates the overall structure of a system into components and their interconnections
 - Software structuring criteria are heuristics or guidelines used to help a designer systematically structure and decompose a software system into its components
 Kiểm chứng: Tôi nhận thấy code AI đã phát biểu định nghĩa đúng theo như thông tin trong sách .</t>
+  </si>
+  <si>
+    <t>COMMET method</t>
+  </si>
+  <si>
+    <t>Class Diagram – Overview</t>
+  </si>
+  <si>
+    <t>What is a Class Diagram in UML? Explain its purpose and main components (Class, Attributes, Methods, Relationships) with an example.</t>
+  </si>
+  <si>
+    <t>Associations &amp; Multiplicity</t>
+  </si>
+  <si>
+    <t>In a Class Diagram, explain Association and Multiplicity. Give examples of 1-1, 1-n, 0..1, n-n relationships.</t>
+  </si>
+  <si>
+    <t>AI response: Association is a static relationship between classes. Multiplicity defines how many instances participate:
+- 1-1: One Person has one Passport
+- 1-n: One Teacher teaches many Students
+- 0..1: A Customer optionally has one Address
+- n-n: Students enroll in many Courses and vice versa
+Reflection: Đúng. Multiplicity rất quan trọng khi thiết kế DB schema. Mình sẽ luyện thêm bằng cách vẽ diagram cho ví dụ thực tế.</t>
+  </si>
+  <si>
+    <t>Composition vs Aggregation</t>
+  </si>
+  <si>
+    <t>What is the difference between Composition and Aggregation in a Class Diagram? Provide a real-world example for each.</t>
+  </si>
+  <si>
+    <t>AI response:
+- Composition (strong "part-of"): Parts cannot exist without the whole. Ex: House → Room. If House is destroyed, Rooms are too.
+- Aggregation (weak "part-of"): Parts can exist independently. Ex: Library → Book. A Book can exist without a Library.
+Reflection: Kiểm chứng đúng với sách Gomaa Ch.7. Composition dùng diamond đặc (♦), Aggregation dùng diamond rỗng (◇). Sẽ chú ý khi vẽ diagram.</t>
+  </si>
+  <si>
+    <t>Generalization / Inheritance</t>
+  </si>
+  <si>
+    <t>Explain Generalization/Specialization in Class Diagrams. How does a Subclass inherit from a Superclass? Give an example.</t>
+  </si>
+  <si>
+    <t>AI response: Generalization is the "is-a" relationship. A Subclass inherits all attributes and methods from its Superclass and can add its own.
+Example: Animal (superclass) → Dog, Cat (subclasses). Dog inherits breathe() from Animal and adds bark().
+Reflection: Phản hồi AI đúng. Inheritance giảm code duplication nhưng cần cẩn thận với deep inheritance trees (khó maintain). Abstract classes cũng được mô hình hóa ở đây.</t>
+  </si>
+  <si>
+    <t>Association Class</t>
+  </si>
+  <si>
+    <t>What is an Association Class? When should you use it? Provide an example with an n-n relationship.</t>
+  </si>
+  <si>
+    <t>AI response: An Association Class is a class attached to an association to hold attributes that belong to the relationship itself, not to either class.
+Example: Student — [Enrollment: grade, date] — Course. The grade belongs to the enrollment event, not to Student or Course alone.
+Reflection: Kiểm chứng đúng với Ch.7. Hay dùng trong quan hệ n-n khi có thuộc tính phụ thuộc vào chính mối quan hệ đó.</t>
+  </si>
+  <si>
+    <t>System Context Modeling</t>
+  </si>
+  <si>
+    <t>What is System Context Modeling in Static Design? Explain Total System Context vs Software System Context.</t>
+  </si>
+  <si>
+    <t>AI response:
+- Total System Context: Includes hardware + software boundaries. Shows external devices, users, timers and how they interact with the whole system.
+- Software System Context: Focuses only on the software boundary. External entities are modeled using stereotypes: «external user», «external system», «external input device», «external timer».
+Reflection: Đúng với Ch.7. Bước này quan trọng để xác định scope của hệ thống trước khi thiết kế chi tiết. Tránh thiết kế những gì nằm ngoài boundary.</t>
+  </si>
+  <si>
+    <t>Entity Class</t>
+  </si>
+  <si>
+    <t>What is an Entity Class? How does it differ from other class types in system design?</t>
+  </si>
+  <si>
+    <t>AI response: An Entity Class represents a real-world concept that the system needs to track. It typically:
+- Holds significant persistent data (stored long-term)
+- Maps closely to database tables
+- Has minimal behavior (mostly getter/setter operations)
+Example: Customer, Order, Product.
+Reflection: Đúng. Entity Class ≠ Control Class (which coordinates logic) ≠ Boundary Class (which interfaces with outside). Đây là nền tảng để hiểu Object Structuring ở Ch.8.</t>
+  </si>
+  <si>
+    <t>Use Case – Overview &amp; Purpose</t>
+  </si>
+  <si>
+    <t>What is a Use Case in UML? What is its purpose in Requirements Modeling? (Gomaa Ch.6)</t>
+  </si>
+  <si>
+    <t>AI response: A Use Case describes a complete sequence of interactions between an Actor and a system to achieve a specific goal. It captures functional requirements from a 'black box' perspective — what the system does, not how.
+Example: Use Case 'Withdraw Cash' between Actor 'Customer' and ATM system.
+Reflection: Đúng. Use Case giúp xác định yêu cầu chức năng mà không cần biết bên trong hệ thống làm gì. 'Black box view' rất quan trọng ở giai đoạn phân tích. Mình phân biệt: Use Case ≠ User Story (Agile) — Use Case chi tiết hơn, có luồng chính và nhánh.</t>
+  </si>
+  <si>
+    <t>Actor – Các loại tác nhân</t>
+  </si>
+  <si>
+    <t>In Use Case Modeling, what is an Actor? List and explain all types of Actors with examples. (Gomaa Ch.6)</t>
+  </si>
+  <si>
+    <t>AI response: An Actor is an entity outside the system that interacts with it.
+Types:
+- Primary Actor: Initiates the use case (e.g., Customer places order)
+- Secondary Actor: Supports the use case (e.g., Payment Gateway)
+- Human Actor: A person (e.g., Admin, Customer)
+- External System Actor: Another system (e.g., Bank API)
+- Input Device Actor: Hardware input (e.g., Sensor, Card Reader)
+- Timer Actor: Triggers use case by time (e.g., Scheduler running at midnight)
+Reflection: Đúng hoàn toàn với Ch.6. Timer Actor hay bị quên — quan trọng trong real-time/embedded systems. Secondary Actor không khởi tạo use case nhưng cần thiết để hoàn thành nó.</t>
+  </si>
+  <si>
+    <t>Main Sequence &amp; Alternative Sequences</t>
+  </si>
+  <si>
+    <t>What is the Main Sequence in a Use Case? What are Alternative Sequences? Give an example of both. (Gomaa Ch.6)</t>
+  </si>
+  <si>
+    <t>AI response: 
+- Main Sequence (Happy Path): The normal, successful flow of steps.
+  Ex: Customer logs in → selects item → pays → receives confirmation.
+- Alternative Sequences: Deviations from the main path (errors, exceptions, options).
+  Ex: Payment fails → system shows error → customer retries or cancels.
+Reflection: Kiểm chứng đúng. Alternative Sequences mô tả edge cases — rất quan trọng cho testing. Trong UML, alternative sequences thường được ghi dưới dạng 'Extension Points' hoặc alt fragments trong sequence diagrams.</t>
+  </si>
+  <si>
+    <t>Activity Diagram</t>
+  </si>
+  <si>
+    <t>What is an Activity Diagram? How is it used in Use Case Modeling? When should you use it over a simple flow description? (Gomaa Ch.6)</t>
+  </si>
+  <si>
+    <t>AI response: An Activity Diagram is a UML behavioral diagram that shows the flow of control inside a Use Case using actions, decisions (branches), forks (parallel flows), and merge nodes.
+Use when: The use case has complex logic, multiple branches, or parallel steps that are hard to describe in plain text.
+Example: 'Process Online Order' — shows branches for in-stock vs out-of-stock, parallel payment and inventory check.
+Reflection: Đúng. Activity Diagram = flowchart nâng cao trong UML. Dùng để visualize luồng phức tạp trong 1 Use Case, không phải để mô tả tương tác giữa các objects (đó là Sequence Diagram).</t>
+  </si>
+  <si>
+    <t>Functional vs Non-Functional Requirements</t>
+  </si>
+  <si>
+    <t>In Requirements Modeling, what is the difference between Functional and Non-Functional requirements? Give examples of each. (Gomaa Ch.6)</t>
+  </si>
+  <si>
+    <t>AI response:
+- Functional Requirements: What the system must DO.
+  Ex: The system shall allow users to reset their password via email.
+- Non-Functional Requirements (Quality Attributes): How well the system performs.
+  Ex: The system shall respond to login requests within 2 seconds (Performance). The system shall be available 99.9% of the time (Reliability).
+Reflection: Đúng. Use Cases chủ yếu capture Functional Requirements. Non-Functional requirements thường được ghi riêng (constraints). Cả hai đều cần thiết trong Requirements Modeling phase.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,6 +250,18 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -142,10 +296,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -171,9 +326,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{32FF6209-8230-4EBE-A6D5-9B042AC8CC20}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -505,28 +676,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
     <col min="3" max="3" width="68.42578125" customWidth="1"/>
     <col min="4" max="4" width="67" customWidth="1"/>
-    <col min="5" max="5" width="78.5703125" customWidth="1"/>
+    <col min="5" max="5" width="70.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="E1" s="1"/>
     </row>
@@ -535,16 +706,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="120" x14ac:dyDescent="0.25">
@@ -552,13 +723,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>13</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>16</v>
       </c>
       <c r="E3" s="8"/>
     </row>
@@ -567,30 +738,189 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E4" s="8"/>
     </row>
-    <row r="5" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="B5" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="E5" s="8"/>
+      <c r="B9" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
